--- a/hoagland_recipes/NxPxI_hoagland_lowN.xlsx
+++ b/hoagland_recipes/NxPxI_hoagland_lowN.xlsx
@@ -21,7 +21,7 @@
     <sheet name="0 ppm N, 62 ppm P" sheetId="8" r:id="rId6"/>
     <sheet name="0 ppm N, 93 ppm P" sheetId="9" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1252,28 +1252,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">

--- a/hoagland_recipes/NxPxI_hoagland_lowN.xlsx
+++ b/hoagland_recipes/NxPxI_hoagland_lowN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eaperkowski/git/2026_NxPxI/hoagland_recipes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{180F8E55-65CF-E746-98DB-1D0D8E668ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A3B9F72-513B-6349-B078-241C9D5315FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1740" yWindow="660" windowWidth="28500" windowHeight="18980" activeTab="6" xr2:uid="{EA5B7CD4-0592-B14D-A568-E53194DF6487}"/>
+    <workbookView xWindow="40300" yWindow="5200" windowWidth="28500" windowHeight="18980" activeTab="2" xr2:uid="{EA5B7CD4-0592-B14D-A568-E53194DF6487}"/>
   </bookViews>
   <sheets>
     <sheet name="Stock solutions" sheetId="1" r:id="rId1"/>
@@ -2348,19 +2348,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{516136DE-12C0-BC4C-B963-A9701A317B59}">
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>18</v>
       </c>
       <c r="B1" s="8"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -2377,7 +2377,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -2411,7 +2411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -2428,7 +2428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -2445,12 +2445,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -2467,7 +2467,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -2484,8 +2484,12 @@
         <f>(C10*1000)/(1000/(B10*D10))</f>
         <v>34.021500000000003</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F10">
+        <f t="shared" ref="F10:F15" si="0">D10*2</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -2502,8 +2506,12 @@
         <f>(C11*1000)/(1000/(B11*D11))</f>
         <v>279.58124999999995</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -2517,11 +2525,15 @@
         <v>4</v>
       </c>
       <c r="E12" s="9">
-        <f t="shared" ref="E12:E15" si="0">(C12*1000)/(1000/(B12*D12))</f>
+        <f t="shared" ref="E12:E15" si="1">(C12*1000)/(1000/(B12*D12))</f>
         <v>400.34800000000001</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -2535,11 +2547,15 @@
         <v>1</v>
       </c>
       <c r="E13" s="9">
+        <f t="shared" si="1"/>
+        <v>492.96</v>
+      </c>
+      <c r="F13">
         <f t="shared" si="0"/>
-        <v>492.96</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -2550,8 +2566,12 @@
         <v>1</v>
       </c>
       <c r="E14" s="9"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -2562,8 +2582,12 @@
         <v>1</v>
       </c>
       <c r="E15" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -2729,7 +2753,7 @@
         <v>0.25</v>
       </c>
       <c r="E26" s="9">
-        <f t="shared" ref="E26:E32" si="1">(C26*1000)/(1000/(B26*D26))</f>
+        <f t="shared" ref="E26:E32" si="2">(C26*1000)/(1000/(B26*D26))</f>
         <v>9.7735749999999992</v>
       </c>
     </row>
@@ -2748,7 +2772,7 @@
         <v>0.25</v>
       </c>
       <c r="E27" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.7434250000000002</v>
       </c>
     </row>
@@ -2767,7 +2791,7 @@
         <v>3.75</v>
       </c>
       <c r="E28" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>146.60362499999997</v>
       </c>
     </row>
@@ -2786,7 +2810,7 @@
         <v>3.75</v>
       </c>
       <c r="E29" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>132.94874999999999</v>
       </c>
     </row>
@@ -2805,7 +2829,7 @@
         <v>4</v>
       </c>
       <c r="E30" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>160.31200000000001</v>
       </c>
     </row>
@@ -2824,7 +2848,7 @@
         <v>1</v>
       </c>
       <c r="E31" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>48.61</v>
       </c>
     </row>
@@ -2843,7 +2867,7 @@
         <v>1</v>
       </c>
       <c r="E32" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>64.13</v>
       </c>
     </row>
@@ -2925,19 +2949,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC620572-E7E9-C149-A071-72B5F47728B3}">
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>18</v>
       </c>
       <c r="B1" s="8"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -2954,7 +2978,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -2971,7 +2995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -2988,7 +3012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -3005,7 +3029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -3022,12 +3046,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -3044,7 +3068,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -3061,8 +3085,12 @@
         <f>(C10*1000)/(1000/(B10*D10))</f>
         <v>68.043000000000006</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F10">
+        <f>D10*2</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -3079,8 +3107,12 @@
         <f>(C11*1000)/(1000/(B11*D11))</f>
         <v>260.9425</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="F11">
+        <f t="shared" ref="F11:F15" si="0">D11*2</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -3094,11 +3126,15 @@
         <v>4</v>
       </c>
       <c r="E12" s="9">
-        <f t="shared" ref="E12:E15" si="0">(C12*1000)/(1000/(B12*D12))</f>
+        <f t="shared" ref="E12:E15" si="1">(C12*1000)/(1000/(B12*D12))</f>
         <v>400.34800000000001</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -3112,11 +3148,15 @@
         <v>1</v>
       </c>
       <c r="E13" s="9">
+        <f t="shared" si="1"/>
+        <v>492.96</v>
+      </c>
+      <c r="F13">
         <f t="shared" si="0"/>
-        <v>492.96</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -3127,8 +3167,12 @@
         <v>1</v>
       </c>
       <c r="E14" s="9"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -3139,8 +3183,12 @@
         <v>1</v>
       </c>
       <c r="E15" s="9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -3306,7 +3354,7 @@
         <v>0.5</v>
       </c>
       <c r="E26" s="9">
-        <f t="shared" ref="E26:E32" si="1">(C26*1000)/(1000/(B26*D26))</f>
+        <f t="shared" ref="E26:E32" si="2">(C26*1000)/(1000/(B26*D26))</f>
         <v>19.547149999999998</v>
       </c>
     </row>
@@ -3325,7 +3373,7 @@
         <v>0.5</v>
       </c>
       <c r="E27" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15.48685</v>
       </c>
     </row>
@@ -3344,7 +3392,7 @@
         <v>3.5</v>
       </c>
       <c r="E28" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>136.83004999999997</v>
       </c>
     </row>
@@ -3363,7 +3411,7 @@
         <v>3.5</v>
       </c>
       <c r="E29" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>124.0855</v>
       </c>
     </row>
@@ -3382,7 +3430,7 @@
         <v>4</v>
       </c>
       <c r="E30" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>160.31200000000001</v>
       </c>
     </row>
@@ -3401,7 +3449,7 @@
         <v>1</v>
       </c>
       <c r="E31" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>48.61</v>
       </c>
     </row>
@@ -3420,7 +3468,7 @@
         <v>1</v>
       </c>
       <c r="E32" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>64.13</v>
       </c>
     </row>

--- a/hoagland_recipes/NxPxI_hoagland_lowN.xlsx
+++ b/hoagland_recipes/NxPxI_hoagland_lowN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eaperkowski/git/2026_NxPxI/hoagland_recipes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A3B9F72-513B-6349-B078-241C9D5315FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EDC4C00-1C3C-3745-A36E-307964F0E0D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40300" yWindow="5200" windowWidth="28500" windowHeight="18980" activeTab="2" xr2:uid="{EA5B7CD4-0592-B14D-A568-E53194DF6487}"/>
+    <workbookView xWindow="40300" yWindow="600" windowWidth="28500" windowHeight="18980" activeTab="1" xr2:uid="{EA5B7CD4-0592-B14D-A568-E53194DF6487}"/>
   </bookViews>
   <sheets>
     <sheet name="Stock solutions" sheetId="1" r:id="rId1"/>
